--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 03/front/Panel 03 report.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 03/front/Panel 03 report.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.64037</v>
+        <v>16.85384</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59674</v>
+        <v>16.33638</v>
       </c>
       <c r="E2" t="n">
-        <v>16.657</v>
+        <v>16.51365</v>
       </c>
       <c r="F2" t="n">
-        <v>42.28188</v>
+        <v>41.54045</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05014</v>
+        <v>0.04966</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79002</v>
+        <v>1.83749</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.70106</v>
+        <v>16.80699</v>
       </c>
       <c r="D3" t="n">
-        <v>16.40152</v>
+        <v>16.50938</v>
       </c>
       <c r="E3" t="n">
-        <v>16.89043</v>
+        <v>16.62802</v>
       </c>
       <c r="F3" t="n">
-        <v>41.38672</v>
+        <v>41.12171</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04938</v>
+        <v>0.05043</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80479</v>
+        <v>1.82527</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.37912</v>
+        <v>16.79386</v>
       </c>
       <c r="D4" t="n">
-        <v>16.47468</v>
+        <v>16.23575</v>
       </c>
       <c r="E4" t="n">
-        <v>16.19762</v>
+        <v>16.43816</v>
       </c>
       <c r="F4" t="n">
-        <v>42.3119</v>
+        <v>41.41335</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04962</v>
+        <v>0.04982</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79573</v>
+        <v>1.81538</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.65886</v>
+        <v>16.34609</v>
       </c>
       <c r="D5" t="n">
-        <v>16.29498</v>
+        <v>16.23846</v>
       </c>
       <c r="E5" t="n">
-        <v>16.55761</v>
+        <v>16.28419</v>
       </c>
       <c r="F5" t="n">
-        <v>42.79048</v>
+        <v>41.61447</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05056</v>
+        <v>0.0496</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80371</v>
+        <v>1.83528</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.52595</v>
+        <v>16.68998</v>
       </c>
       <c r="D6" t="n">
-        <v>16.66466</v>
+        <v>16.57349</v>
       </c>
       <c r="E6" t="n">
-        <v>16.56524</v>
+        <v>16.62215</v>
       </c>
       <c r="F6" t="n">
-        <v>42.30836</v>
+        <v>41.85071</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04993</v>
+        <v>0.05082</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81683</v>
+        <v>1.77956</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.90606</v>
+        <v>16.72846</v>
       </c>
       <c r="D7" t="n">
-        <v>16.66276</v>
+        <v>16.54349</v>
       </c>
       <c r="E7" t="n">
-        <v>16.70875</v>
+        <v>16.62828</v>
       </c>
       <c r="F7" t="n">
-        <v>42.00633</v>
+        <v>41.43863</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0506</v>
+        <v>0.05052</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81278</v>
+        <v>1.79057</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.60377</v>
+        <v>16.57409</v>
       </c>
       <c r="D8" t="n">
-        <v>16.51821</v>
+        <v>16.26896</v>
       </c>
       <c r="E8" t="n">
-        <v>16.27697</v>
+        <v>16.5378</v>
       </c>
       <c r="F8" t="n">
-        <v>41.57435</v>
+        <v>41.86441</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05071</v>
+        <v>0.0502</v>
       </c>
       <c r="H8" t="n">
-        <v>1.78263</v>
+        <v>1.83329</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.81858</v>
+        <v>16.46936</v>
       </c>
       <c r="D9" t="n">
-        <v>16.37169</v>
+        <v>16.34566</v>
       </c>
       <c r="E9" t="n">
-        <v>16.45163</v>
+        <v>16.4543</v>
       </c>
       <c r="F9" t="n">
-        <v>41.54846</v>
+        <v>41.14576</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05014</v>
+        <v>0.04926</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81591</v>
+        <v>1.78883</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.25077</v>
+        <v>16.69606</v>
       </c>
       <c r="D10" t="n">
-        <v>16.28156</v>
+        <v>16.33613</v>
       </c>
       <c r="E10" t="n">
-        <v>16.46816</v>
+        <v>16.61638</v>
       </c>
       <c r="F10" t="n">
-        <v>42.10288</v>
+        <v>42.35638</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04918</v>
+        <v>0.04995</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83305</v>
+        <v>1.814</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59109</v>
+        <v>0.60434</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1268</v>
+        <v>1.08938</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.58591</v>
+        <v>0.59108</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10202</v>
+        <v>1.09131</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6122300000000001</v>
+        <v>0.61304</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11737</v>
+        <v>1.10047</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59802</v>
+        <v>0.61675</v>
       </c>
       <c r="D15" t="n">
-        <v>1.11258</v>
+        <v>1.09328</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.61534</v>
+        <v>0.59984</v>
       </c>
       <c r="D16" t="n">
-        <v>1.08922</v>
+        <v>1.10566</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.60173</v>
+        <v>0.60102</v>
       </c>
       <c r="D17" t="n">
-        <v>1.11247</v>
+        <v>1.11504</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.59828</v>
+        <v>0.59853</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08717</v>
+        <v>1.10471</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.59082</v>
+        <v>0.59956</v>
       </c>
       <c r="D19" t="n">
-        <v>1.08752</v>
+        <v>1.10664</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60083</v>
+        <v>0.60138</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10401</v>
+        <v>1.11076</v>
       </c>
     </row>
   </sheetData>
